--- a/research/output_charts/ar_change_multihorizon_tables.xlsx
+++ b/research/output_charts/ar_change_multihorizon_tables.xlsx
@@ -10,8 +10,9 @@
     <sheet name="Brier" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="AUC" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="HighVol_Detection" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="DM_Tests" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Dissertation_Table" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Hit_vs_AlwaysCalm" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="DM_Tests" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Dissertation_Table" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -460,27 +461,27 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0.0907</t>
+          <t>0.1124</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.0904</t>
+          <t>0.1086</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.1205</t>
+          <t>0.1410</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>24.7%</t>
+          <t>20.3%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>23.0%</t>
         </is>
       </c>
     </row>
@@ -492,27 +493,27 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0.0993</t>
+          <t>0.1246</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.0977</t>
+          <t>0.1154</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.1312</t>
+          <t>0.1500</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>24.3%</t>
+          <t>16.9%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>25.5%</t>
+          <t>23.1%</t>
         </is>
       </c>
     </row>
@@ -524,27 +525,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.1058</t>
+          <t>0.1419</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.1101</t>
+          <t>0.1221</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.1382</t>
+          <t>0.1650</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>23.4%</t>
+          <t>14.0%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>20.3%</t>
+          <t>26.0%</t>
         </is>
       </c>
     </row>
@@ -602,27 +603,27 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0.8082</t>
+          <t>0.8157</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.7980</t>
+          <t>0.8140</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.7354</t>
+          <t>0.7535</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>+1.0pp</t>
+          <t>+0.2pp</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>+7.3pp</t>
+          <t>+6.2pp</t>
         </is>
       </c>
     </row>
@@ -634,27 +635,27 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0.7659</t>
+          <t>0.7821</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.7382</t>
+          <t>0.7796</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.6948</t>
+          <t>0.7345</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>+2.8pp</t>
+          <t>+0.2pp</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>+7.1pp</t>
+          <t>+4.8pp</t>
         </is>
       </c>
     </row>
@@ -666,27 +667,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.7510</t>
+          <t>0.7455</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.6021</t>
+          <t>0.6947</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.6677</t>
+          <t>0.6891</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>+14.9pp</t>
+          <t>+5.1pp</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>+8.3pp</t>
+          <t>+5.6pp</t>
         </is>
       </c>
     </row>
@@ -734,17 +735,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>36.1%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>20.1%</t>
+          <t>45.9%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>40.4%</t>
+          <t>42.0%</t>
         </is>
       </c>
     </row>
@@ -756,17 +757,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>31.8%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>6.7%</t>
+          <t>36.2%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>34.9%</t>
+          <t>40.1%</t>
         </is>
       </c>
     </row>
@@ -778,17 +779,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>38.4%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>15.9%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>31.7%</t>
+          <t>34.1%</t>
         </is>
       </c>
     </row>
@@ -803,7 +804,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -814,32 +815,27 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>DM (Change vs RW)</t>
+          <t>Always-Calm</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>p-value</t>
+          <t>AR Change</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Change Wins?</t>
+          <t>AR Baseline</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>DM (Change vs Baseline)</t>
+          <t>Random Walk</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t xml:space="preserve">p-value </t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Change Wins? </t>
+          <t>Change - Always-Calm</t>
         </is>
       </c>
     </row>
@@ -851,32 +847,27 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>-10.432</t>
+          <t>85.20%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>&lt;0.0001</t>
+          <t>86.24%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Yes***</t>
+          <t>86.71%</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2.021</t>
+          <t>82.85%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0.0432</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>No**</t>
+          <t>+1.04pp</t>
         </is>
       </c>
     </row>
@@ -888,32 +879,27 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>-11.015</t>
+          <t>85.30%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>&lt;0.0001</t>
+          <t>85.39%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Yes***</t>
+          <t>85.63%</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.966</t>
+          <t>82.28%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0.0493</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>No**</t>
+          <t>+0.09pp</t>
         </is>
       </c>
     </row>
@@ -925,32 +911,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-9.781</t>
+          <t>85.77%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>&lt;0.0001</t>
+          <t>82.80%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Yes***</t>
+          <t>84.59%</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>-0.135</t>
+          <t>80.68%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0.8923</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Yes</t>
+          <t>-2.97pp</t>
         </is>
       </c>
     </row>
@@ -965,7 +946,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -976,47 +957,32 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>DM (Change vs RW)</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Brier (Change)</t>
+          <t>p-value</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Brier (Baseline)</t>
+          <t>Change Wins?</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Brier (RW)</t>
+          <t>DM (Change vs Baseline)</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Skill (Change)</t>
+          <t xml:space="preserve">p-value </t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>AUC (Change)</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>AUC (Baseline)</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>AUC (RW)</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>HighVol Det.</t>
+          <t xml:space="preserve">Change Wins? </t>
         </is>
       </c>
     </row>
@@ -1026,47 +992,34 @@
           <t>1-day</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>3310</v>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>-5.952</t>
+        </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.0907</t>
+          <t>&lt;0.0001</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.0904</t>
+          <t>Yes***</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.1205</t>
+          <t>3.543</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>24.7%</t>
+          <t>0.0004</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0.808</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0.798</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>0.735</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>36.1%</t>
+          <t>No***</t>
         </is>
       </c>
     </row>
@@ -1076,47 +1029,34 @@
           <t>5-day</t>
         </is>
       </c>
-      <c r="B3" t="n">
-        <v>3310</v>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>-6.105</t>
+        </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.0993</t>
+          <t>&lt;0.0001</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.0977</t>
+          <t>Yes***</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.1312</t>
+          <t>4.263</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>24.3%</t>
+          <t>&lt;0.0001</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0.766</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0.738</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>0.695</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>31.8%</t>
+          <t>No***</t>
         </is>
       </c>
     </row>
@@ -1126,47 +1066,310 @@
           <t>21-day</t>
         </is>
       </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>-3.473</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>0.0005</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Yes***</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>2.208</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>0.0272</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>No**</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Horizon</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Brier (Change)</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Brier (Baseline)</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Brier (RW)</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Skill (Change)</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>AUC (Change)</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>AUC (Baseline)</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>AUC (RW)</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>HighVol Det.</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Hit Rate (Change)</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Hit Rate (Always-Calm)</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Hit Gain vs Always-Calm</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1-day</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2122</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>0.1124</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>0.1086</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0.1410</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>20.3%</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0.816</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0.814</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>0.753</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>86.2%</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>85.2%</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>+1.0pp</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>5-day</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2122</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>0.1246</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>0.1154</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0.1500</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>16.9%</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0.782</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0.780</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>0.735</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>45.8%</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>85.4%</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>85.3%</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>+0.1pp</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>21-day</t>
+        </is>
+      </c>
       <c r="B4" t="n">
-        <v>3310</v>
+        <v>2122</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.1058</t>
+          <t>0.1419</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.1101</t>
+          <t>0.1221</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.1382</t>
+          <t>0.1650</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>23.4%</t>
+          <t>14.0%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0.751</t>
+          <t>0.746</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.602</t>
+          <t>0.695</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.668</t>
+          <t>0.689</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>38.4%</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>82.8%</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>85.8%</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>-3.0pp</t>
         </is>
       </c>
     </row>

--- a/research/output_charts/ar_change_multihorizon_tables.xlsx
+++ b/research/output_charts/ar_change_multihorizon_tables.xlsx
@@ -461,27 +461,27 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0.1124</t>
+          <t>0.1165</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.1086</t>
+          <t>0.1110</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.1410</t>
+          <t>0.1428</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>20.3%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>23.0%</t>
+          <t>22.3%</t>
         </is>
       </c>
     </row>
@@ -493,27 +493,27 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0.1246</t>
+          <t>0.1308</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.1154</t>
+          <t>0.1168</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.1500</t>
+          <t>0.1554</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>16.9%</t>
+          <t>15.8%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>24.9%</t>
         </is>
       </c>
     </row>
@@ -525,22 +525,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.1419</t>
+          <t>0.1358</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.1221</t>
+          <t>0.1169</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.1650</t>
+          <t>0.1581</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>14.0%</t>
+          <t>14.1%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -603,27 +603,27 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0.8157</t>
+          <t>0.7957</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.8140</t>
+          <t>0.7953</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.7535</t>
+          <t>0.7294</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>+0.2pp</t>
+          <t>+0.0pp</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>+6.2pp</t>
+          <t>+6.6pp</t>
         </is>
       </c>
     </row>
@@ -635,27 +635,27 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0.7821</t>
+          <t>0.7577</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.7796</t>
+          <t>0.7519</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.7345</t>
+          <t>0.6954</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>+0.2pp</t>
+          <t>+0.6pp</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>+4.8pp</t>
+          <t>+6.2pp</t>
         </is>
       </c>
     </row>
@@ -667,27 +667,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.7455</t>
+          <t>0.7486</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.6947</t>
+          <t>0.7048</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.6891</t>
+          <t>0.7018</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>+5.1pp</t>
+          <t>+4.4pp</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>+5.6pp</t>
+          <t>+4.7pp</t>
         </is>
       </c>
     </row>
@@ -735,17 +735,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>42.2%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>45.9%</t>
+          <t>34.7%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>42.0%</t>
+          <t>39.2%</t>
         </is>
       </c>
     </row>
@@ -757,17 +757,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>45.8%</t>
+          <t>36.8%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>36.2%</t>
+          <t>28.1%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>40.1%</t>
+          <t>34.5%</t>
         </is>
       </c>
     </row>
@@ -779,17 +779,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>38.4%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>15.9%</t>
+          <t>13.1%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>34.1%</t>
+          <t>32.6%</t>
         </is>
       </c>
     </row>
@@ -847,27 +847,27 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>85.20%</t>
+          <t>85.72%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>86.24%</t>
+          <t>84.81%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>86.71%</t>
+          <t>85.64%</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>82.85%</t>
+          <t>82.65%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>+1.04pp</t>
+          <t>-0.91pp</t>
         </is>
       </c>
     </row>
@@ -879,27 +879,27 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>85.30%</t>
+          <t>85.70%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>85.39%</t>
+          <t>83.28%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>85.63%</t>
+          <t>85.40%</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>82.28%</t>
+          <t>81.28%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>+0.09pp</t>
+          <t>-2.42pp</t>
         </is>
       </c>
     </row>
@@ -911,27 +911,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>85.77%</t>
+          <t>85.72%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>82.80%</t>
+          <t>82.83%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>84.59%</t>
+          <t>85.83%</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>80.68%</t>
+          <t>80.75%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-2.97pp</t>
+          <t>-2.89pp</t>
         </is>
       </c>
     </row>
@@ -994,7 +994,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>-5.952</t>
+          <t>-9.006</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>3.543</t>
+          <t>4.754</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0.0004</t>
+          <t>&lt;0.0001</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -1031,7 +1031,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>-6.105</t>
+          <t>-10.191</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>4.263</t>
+          <t>7.592</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1068,12 +1068,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-3.473</t>
+          <t>-6.315</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.0005</t>
+          <t>&lt;0.0001</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1083,17 +1083,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2.208</t>
+          <t>3.163</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0.0272</t>
+          <t>0.0016</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>No**</t>
+          <t>No***</t>
         </is>
       </c>
     </row>
@@ -1185,61 +1185,61 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2122</v>
+        <v>4748</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.1124</t>
+          <t>0.1165</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.1086</t>
+          <t>0.1110</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.1410</t>
+          <t>0.1428</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>20.3%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0.816</t>
+          <t>0.796</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0.814</t>
+          <t>0.795</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.753</t>
+          <t>0.729</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>42.2%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>86.2%</t>
+          <t>84.8%</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>85.2%</t>
+          <t>85.7%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>+1.0pp</t>
+          <t>-0.9pp</t>
         </is>
       </c>
     </row>
@@ -1250,61 +1250,61 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2122</v>
+        <v>4748</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.1246</t>
+          <t>0.1308</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.1154</t>
+          <t>0.1168</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.1500</t>
+          <t>0.1554</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>16.9%</t>
+          <t>15.8%</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0.782</t>
+          <t>0.758</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.780</t>
+          <t>0.752</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.735</t>
+          <t>0.695</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>45.8%</t>
+          <t>36.8%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>85.4%</t>
+          <t>83.3%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>85.3%</t>
+          <t>85.7%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>+0.1pp</t>
+          <t>-2.4pp</t>
         </is>
       </c>
     </row>
@@ -1315,46 +1315,46 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2122</v>
+        <v>4748</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.1419</t>
+          <t>0.1358</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.1221</t>
+          <t>0.1169</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.1650</t>
+          <t>0.1581</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>14.0%</t>
+          <t>14.1%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0.746</t>
+          <t>0.749</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.695</t>
+          <t>0.705</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.689</t>
+          <t>0.702</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>38.4%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1364,12 +1364,12 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>85.8%</t>
+          <t>85.7%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>-3.0pp</t>
+          <t>-2.9pp</t>
         </is>
       </c>
     </row>
